--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A14432D0-619F-459E-9A7B-C41277E151BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252DD398-66DB-4F25-9686-C0B2A4F844CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>1明細毎に削除する機能</t>
     <rPh sb="1" eb="3">
@@ -58,13 +58,6 @@
     <t>内容</t>
     <rPh sb="0" eb="2">
       <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>対応</t>
-    <rPh sb="0" eb="2">
-      <t>タイオウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -155,6 +148,65 @@
 * 段階的移行</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>日付の初期値をsysdate</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ショキチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>検索機能が上</t>
+    <rPh sb="0" eb="4">
+      <t>ケンサクキノウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ウエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>価格は通常とセールの２つにする</t>
+    <rPh sb="0" eb="2">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>検索項目も入力サポート機能を入れる</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対応日</t>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -191,20 +243,41 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -213,14 +286,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -231,6 +301,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,45 +625,178 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FE30FC-11F3-410C-9482-0A4C3F5D7DD0}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
     <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="2.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>46152</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>46158</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6">
+        <v>46158</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="5">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6">
+        <v>46158</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46152</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="C7" s="6">
+        <v>46158</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="5">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="5">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="5">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="5">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="5">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="5">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="5">
+        <v>12</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="5">
+        <v>13</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="5">
+        <v>14</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="5">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -597,45 +809,45 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="2.58203125" style="3"/>
-    <col min="3" max="3" width="18.4140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.9140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="2.58203125" style="3"/>
+    <col min="1" max="2" width="2.58203125" style="2"/>
+    <col min="3" max="3" width="18.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.9140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="2.58203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="368" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="368" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252DD398-66DB-4F25-9686-C0B2A4F844CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124DD2CB-37FD-4952-B602-4A4FE28ED3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
@@ -27,22 +27,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
-  <si>
-    <t>1明細毎に削除する機能</t>
-    <rPh sb="1" eb="3">
-      <t>メイサイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ゴト</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -169,16 +153,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>価格は通常とセールの２つにする</t>
-    <rPh sb="0" eb="2">
-      <t>カカク</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ツウジョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>検索項目も入力サポート機能を入れる</t>
     <rPh sb="0" eb="2">
       <t>ケンサク</t>
@@ -204,6 +178,32 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>価格&amp;日付は、通常とセールの２つにする</t>
+    <rPh sb="0" eb="2">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>家族と共有で利用できるようにしたい</t>
+    <rPh sb="0" eb="2">
+      <t>カゾク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>リヨウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -625,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FE30FC-11F3-410C-9482-0A4C3F5D7DD0}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
@@ -637,21 +637,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="E2" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -659,12 +659,14 @@
         <v>1</v>
       </c>
       <c r="C3" s="6">
-        <v>46152</v>
+        <v>46158</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46158</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="5">
@@ -688,10 +690,10 @@
         <v>46158</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" s="6">
-        <v>46158</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -702,19 +704,19 @@
         <v>46158</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46166</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="5">
         <v>5</v>
       </c>
-      <c r="C7" s="6">
-        <v>46158</v>
-      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="5"/>
     </row>
@@ -789,14 +791,6 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="5">
-        <v>15</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -817,18 +811,18 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -836,18 +830,18 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="368" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124DD2CB-37FD-4952-B602-4A4FE28ED3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D1F2D7-30F3-4911-AF42-B15FD3FD5514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -195,15 +195,58 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>家族と共有で利用できるようにしたい</t>
+    <t>id / createdAt/updatedAt / createdBy/updatedBy追加。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>商品名正規化</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>データ構造整理</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Firebase移行(共有利用）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>今のUI改善続ける</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>【重要⑤】削除機能注意</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一覧から遷移する編集画面について、新規登録画面のレイアウトに合わせてほしい</t>
     <rPh sb="0" eb="2">
-      <t>カゾク</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>キョウユウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>リヨウ</t>
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Node.js、ESLintの対応をしたい</t>
+    <rPh sb="15" eb="17">
+      <t>タイオウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -286,7 +329,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -310,6 +353,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,12 +671,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FE30FC-11F3-410C-9482-0A4C3F5D7DD0}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
     <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="2.58203125" style="1"/>
   </cols>
@@ -714,66 +760,100 @@
       <c r="B7" s="5">
         <v>5</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5" t="s">
-        <v>15</v>
+      <c r="C7" s="6">
+        <v>46166</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="C8" s="6">
+        <v>46166</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46167</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="5">
         <v>7</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C9" s="6">
+        <v>46167</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="6">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="5">
         <v>8</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="6">
+        <v>46166</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="5">
         <v>9</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="6">
+        <v>46166</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="5">
         <v>10</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="6">
+        <v>46166</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="5">
         <v>11</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="C13" s="6">
+        <v>46166</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="5">
         <v>12</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="6">
+        <v>46166</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -792,9 +872,26 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="5">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="5">
+        <v>16</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D1F2D7-30F3-4911-AF42-B15FD3FD5514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E15404-13B5-44FB-BF9B-1C78BEA02BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -211,10 +211,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>今のUI改善続ける</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>【重要⑤】削除機能注意</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -247,6 +243,45 @@
     <t>Node.js、ESLintの対応をしたい</t>
     <rPh sb="15" eb="17">
       <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>－</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>まずは実装対応せずに、入力ルールを決めることで対応</t>
+    <rPh sb="3" eb="5">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>←次回は共有化から対応（2026/6/7終了時メモ）</t>
+    <rPh sb="1" eb="3">
+      <t>ジカイ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>キョウユウカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>シュウリョウジ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -286,7 +321,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -296,6 +331,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,7 +370,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -356,6 +397,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -372,6 +422,134 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6BFB923-1393-ED23-BC41-3917C69BB708}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5156200" y="342900"/>
+          <a:ext cx="3492500" cy="1098550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>chromeF12</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>＞コンソールで実行</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>◆ローカルデータ確認</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>localStorage.getItem("dailyPriceRecords");</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>◆ローカルデータ削除</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>localStorage.removeItem("dailyPriceRecords");</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -671,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FE30FC-11F3-410C-9482-0A4C3F5D7DD0}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="2.58203125" style="1"/>
@@ -681,12 +859,12 @@
     <col min="6" max="16384" width="2.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
@@ -700,7 +878,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="5">
         <v>1</v>
       </c>
@@ -714,7 +892,7 @@
         <v>46158</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="5">
         <v>2</v>
       </c>
@@ -728,7 +906,7 @@
         <v>46158</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="5">
         <v>3</v>
       </c>
@@ -742,7 +920,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5">
         <v>4</v>
       </c>
@@ -756,7 +934,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" ht="27" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="5">
         <v>5</v>
       </c>
@@ -764,51 +942,53 @@
         <v>46166</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" ht="27" x14ac:dyDescent="0.55000000000000004">
+        <v>15</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="5">
         <v>6</v>
       </c>
       <c r="C8" s="6">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E8" s="6">
         <v>46167</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" ht="27" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="5">
         <v>7</v>
       </c>
       <c r="C9" s="6">
-        <v>46167</v>
+        <v>46166</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9" s="6">
-        <v>46167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.55000000000000004">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="5">
         <v>8</v>
       </c>
       <c r="C10" s="6">
         <v>46166</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>21</v>
+      <c r="D10" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="5">
         <v>9</v>
       </c>
@@ -816,11 +996,16 @@
         <v>46166</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="5">
         <v>10</v>
       </c>
@@ -828,35 +1013,36 @@
         <v>46166</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="5">
+        <v>17</v>
+      </c>
+      <c r="E12" s="6">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="10">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="11">
         <v>46166</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="5">
         <v>12</v>
       </c>
-      <c r="C14" s="6">
-        <v>46166</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="5">
         <v>13</v>
       </c>
@@ -864,7 +1050,7 @@
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="5">
         <v>14</v>
       </c>
@@ -879,19 +1065,12 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="5">
-        <v>16</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E15404-13B5-44FB-BF9B-1C78BEA02BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CC6363-4B03-4892-98FE-C37822B080A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
@@ -270,7 +270,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>←次回は共有化から対応（2026/6/7終了時メモ）</t>
+    <t>←次回は共有化から対応（2026/6/13終了時メモ）</t>
     <rPh sb="1" eb="3">
       <t>ジカイ</t>
     </rPh>
@@ -280,7 +280,7 @@
     <rPh sb="9" eb="11">
       <t>タイオウ</t>
     </rPh>
-    <rPh sb="20" eb="23">
+    <rPh sb="21" eb="24">
       <t>シュウリョウジ</t>
     </rPh>
     <phoneticPr fontId="2"/>
@@ -986,7 +986,9 @@
       <c r="D10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="6">
+        <v>46186</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="5">

--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CC6363-4B03-4892-98FE-C37822B080A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B04168E-3A91-4FE6-92C5-E62CBB60BE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
   <sheets>
     <sheet name="タスク" sheetId="1" r:id="rId1"/>
     <sheet name="メモ" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -270,7 +271,172 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>←次回は共有化から対応（2026/6/13終了時メモ）</t>
+    <t>②不要</t>
+    <rPh sb="1" eb="3">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>④不要</t>
+    <rPh sb="1" eb="3">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>⑤不要（①へ追記するため）</t>
+    <rPh sb="1" eb="3">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>①1円あたりの容量を追加したい。例えば「通常最安 300円（2.73/円）スギ」とか？</t>
+    <rPh sb="2" eb="3">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヨウリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    表記方法はアドバイスが欲しい。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>③1円あたりの容量を追加したい。例えば「セール最安 198円（x.xx/円）スギ、ぱぱす」とか？</t>
+    <rPh sb="2" eb="3">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヨウリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タト</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サイヤス</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スギ 通常300円（2.73/円）2026/6/27</t>
+    <rPh sb="3" eb="5">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">         セール198円（x.xx/円）2026/6/27</t>
+    <rPh sb="15" eb="16">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ウエルシア 通常320円（x.xx/円）2026/6/27</t>
+    <rPh sb="6" eb="8">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>⑥1円あたりの容量を追加したい。また日付はYYYY/MM/DDのまま表示させたい。例えば下記とか？</t>
+    <rPh sb="2" eb="3">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヨウリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>タト</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>カキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一覧画面から、仕様と容量を削除
+店舗追加後、入力した検索部分に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヨウリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テンポ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>←次回は共有化から対応（2026/6/27終了時メモ）</t>
     <rPh sb="1" eb="3">
       <t>ジカイ</t>
     </rPh>
@@ -436,8 +602,8 @@
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -452,8 +618,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5156200" y="342900"/>
-          <a:ext cx="3492500" cy="1098550"/>
+          <a:off x="5200650" y="342900"/>
+          <a:ext cx="3492500" cy="1416050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -540,10 +706,893 @@
             </a:rPr>
             <a:t>localStorage.removeItem("dailyPriceRecords");</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>◆ローカルデータをクリップボードに</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>copy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>copy(localStorage.getItem("dailyPriceRecords"))</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
             <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
           </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>298291</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>189845</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CEE0461-5128-C2E8-CF61-DC8B6C36D297}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2286117" cy="3359323"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>60739</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>182217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>629478</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>160131</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D2E5059-9ACF-F4BC-2362-DF9A34BA1F05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="60739" y="861391"/>
+          <a:ext cx="1231348" cy="204305"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>60739</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>204305</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>480391</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>71782</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E81A428-D1C5-C02B-5007-FCA8B5E37032}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="60739" y="1109870"/>
+          <a:ext cx="419652" cy="93869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:srgbClr val="0070C0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>436217</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104913</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>60739</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>193261</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4756502A-8C05-5491-3D76-4714401C1AAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="436217" y="1010478"/>
+          <a:ext cx="287131" cy="314740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>②</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>60738</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>143564</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>248477</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>77304</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{746A4A09-D239-8EB5-BF34-AA12866CF20D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="60738" y="1275521"/>
+          <a:ext cx="2175565" cy="160131"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>22086</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>259522</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>110435</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト ボックス 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02D3BFAC-894E-F3C3-1EB2-186A3B7C6D27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1960217" y="1380434"/>
+          <a:ext cx="287131" cy="314740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>③</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>33131</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>110435</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>452783</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>204304</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D6957CE-178D-7370-8C2E-37BA24AD947D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="33131" y="1468783"/>
+          <a:ext cx="419652" cy="93869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:srgbClr val="0070C0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>425173</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>49695</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>49695</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>138044</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト ボックス 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47D9BDBA-CBF6-BD17-D942-2EB06BA7CF2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="425173" y="1408043"/>
+          <a:ext cx="287131" cy="314740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>④</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>143566</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>187739</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>49697</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>165653</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7410902A-E9FA-51B9-540D-41E2D3299D11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="143566" y="2225261"/>
+          <a:ext cx="1231348" cy="204305"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>71783</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>11043</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>358914</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>99392</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="テキスト ボックス 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F7124F5-399B-8814-45E6-54ECE23029C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1397000" y="2048565"/>
+          <a:ext cx="287131" cy="314740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>⑤</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>154609</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>463826</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>121479</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1826870B-8268-91F1-27A6-01081BD928A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="154609" y="2617305"/>
+          <a:ext cx="1634434" cy="673652"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:solidFill>
+            <a:srgbClr val="0070C0"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>314739</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>138042</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>601870</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>226391</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="テキスト ボックス 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35AEB256-8CF2-08A5-25BD-50FD6314920F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1639956" y="2401955"/>
+          <a:ext cx="287131" cy="314740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>⑥</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>557695</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>16564</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>182218</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>104913</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="テキスト ボックス 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF13FF00-DCEC-A2FF-3385-2DC4359E11A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1220304" y="695738"/>
+          <a:ext cx="287131" cy="314740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>①</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -852,7 +1901,8 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="2.58203125" style="1"/>
+    <col min="1" max="1" width="2.58203125" style="1"/>
+    <col min="2" max="2" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1021,28 +2071,34 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="10">
+    <row r="13" spans="1:6" ht="27" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="5">
         <v>11</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="6">
+        <v>46186</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="6">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="10">
+        <v>12</v>
+      </c>
+      <c r="C14" s="11">
         <v>46166</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="5">
-        <v>12</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="5">
@@ -1126,4 +2182,71 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD274FC4-31E2-4417-9354-6D510591CD10}">
+  <dimension ref="E2:F13"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="2" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="5:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B04168E-3A91-4FE6-92C5-E62CBB60BE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE32049-B4E7-4A94-A2CA-2B747DEB4721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -451,6 +451,71 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>初回だけまとめて投入できる仕組み
+importToFirebase.js
+というファイルを作り、
+node importToFirebase.js
+を1回実行するだけ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STEP2
+データを読む
+起動時だけ
+Firestore
+↓
+データ取得
+↓
+画面表示
+ここまで確認します。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STEP1（今回）
+Firebaseに接続できるようにする
+firebase.js を本物の実装にする
+Firestoreに接続する
+動作確認</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STEP3
+登録
+商品登録
+↓
+Firestore保存
+↓
+画面更新</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STEP4
+編集
+↓
+Firestore更新
+↓
+画面更新</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STEP5
+削除
+↓
+Firestore削除
+↓
+画面更新</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STEP6（最後）
+storage.js
+を卒業します。
+つまり
+localStorage
+を完全に無くします。</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -487,7 +552,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -497,12 +562,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -564,13 +623,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1898,7 +1957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FE30FC-11F3-410C-9482-0A4C3F5D7DD0}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="2.58203125" defaultRowHeight="13.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="1"/>
@@ -2095,34 +2154,186 @@
       <c r="D14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="10"/>
+      <c r="E14" s="11">
+        <v>46208</v>
+      </c>
       <c r="F14" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6" ht="67.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="5">
         <v>13</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="5">
+      <c r="C15" s="6">
+        <v>46208</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="6">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="121.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="10">
         <v>14</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="6">
+        <v>46208</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:5" ht="94.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="5">
         <v>15</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="6">
+        <v>46208</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:5" ht="81" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="10">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6">
+        <v>46208</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="2:5" ht="81" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="5">
+        <v>17</v>
+      </c>
+      <c r="C19" s="6">
+        <v>46208</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="2:5" ht="81" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="10">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6">
+        <v>46208</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="2:5" ht="67.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="5">
+        <v>19</v>
+      </c>
+      <c r="C21" s="6">
+        <v>46208</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="10">
+        <v>20</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="5">
+        <v>21</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="10">
+        <v>22</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="5">
+        <v>23</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="10">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="5">
+        <v>25</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="10">
+        <v>26</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="5">
+        <v>27</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="10">
+        <v>28</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="5">
+        <v>29</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="10">
+        <v>30</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE32049-B4E7-4A94-A2CA-2B747DEB4721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F618614-A2FF-4F7E-8F7C-2958CF35A611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -514,6 +514,16 @@
 つまり
 localStorage
 を完全に無くします。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2026/8/22 「Firestoreに接続して、データを読み込める」まで完了。次は「storage.js の保存処理をFirestoreに切り替える」</t>
+    <rPh sb="38" eb="40">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ツギ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -595,7 +605,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -623,15 +633,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -653,16 +654,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4006850</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>215900</xdr:rowOff>
+      <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -677,7 +678,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5200650" y="342900"/>
+          <a:off x="5060950" y="330200"/>
           <a:ext cx="3492500" cy="1416050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1965,7 +1966,8 @@
     <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="2.58203125" style="1"/>
+    <col min="6" max="6" width="53.08203125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="2.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -2144,20 +2146,20 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="10">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="5">
         <v>12</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="6">
         <v>46166</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="6">
         <v>46208</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2176,7 +2178,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="121.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="10">
+      <c r="B16" s="5">
         <v>14</v>
       </c>
       <c r="C16" s="6">
@@ -2186,6 +2188,9 @@
         <v>37</v>
       </c>
       <c r="E16" s="5"/>
+      <c r="F16" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="17" spans="2:5" ht="94.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="5">
@@ -2200,7 +2205,7 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:5" ht="81" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="10">
+      <c r="B18" s="5">
         <v>16</v>
       </c>
       <c r="C18" s="6">
@@ -2224,7 +2229,7 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="2:5" ht="81" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="10">
+      <c r="B20" s="5">
         <v>18</v>
       </c>
       <c r="C20" s="6">
@@ -2248,7 +2253,7 @@
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="10">
+      <c r="B22" s="5">
         <v>20</v>
       </c>
       <c r="C22" s="5"/>
@@ -2264,7 +2269,7 @@
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="10">
+      <c r="B24" s="5">
         <v>22</v>
       </c>
       <c r="C24" s="5"/>
@@ -2280,7 +2285,7 @@
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="10">
+      <c r="B26" s="5">
         <v>24</v>
       </c>
       <c r="C26" s="5"/>
@@ -2296,7 +2301,7 @@
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="10">
+      <c r="B28" s="5">
         <v>26</v>
       </c>
       <c r="C28" s="5"/>
@@ -2312,7 +2317,7 @@
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="10">
+      <c r="B30" s="5">
         <v>28</v>
       </c>
       <c r="C30" s="5"/>
@@ -2328,7 +2333,7 @@
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="10">
+      <c r="B32" s="5">
         <v>30</v>
       </c>
       <c r="C32" s="5"/>

--- a/【メモ】価格記録アプリ.xlsx
+++ b/【メモ】価格記録アプリ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ma_tu\Desktop\Vscode\価格記録アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F618614-A2FF-4F7E-8F7C-2958CF35A611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828BDCE0-292F-4FC8-8C58-7DF805EB5A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CF21DDE-242A-439A-8422-B17E13B6A06F}"/>
   </bookViews>
@@ -703,6 +703,140 @@
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>【Firebase】</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>◆データベース</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>  左メニュー＞</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>Database</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>と</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>Storage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>＞</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>Firestore</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3562350</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="テキスト ボックス 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E1DDA72-01B8-3EA2-98CB-7A8A17B577F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8108950" y="1041400"/>
+          <a:ext cx="3492500" cy="1416050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>【localStorage】</a:t>
+          </a:r>
+        </a:p>
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
